--- a/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
@@ -441,13 +441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO1"/>
+  <dimension ref="A1:AO7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -471,20 +471,20 @@
     <col width="18" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="19" customWidth="1" min="34" max="34"/>
     <col width="23" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="15" customWidth="1" min="38" max="38"/>
     <col width="18" customWidth="1" min="39" max="39"/>
     <col width="15" customWidth="1" min="40" max="40"/>
-    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="44" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -691,6 +691,582 @@
       <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2965</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>ES|Madrid|economy</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Derived from hotel inventory · CoStar doesn't ship class-level KPIs in this drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>luxury</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3869</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>ES|Madrid|luxury</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Derived from hotel inventory · CoStar doesn't ship class-level KPIs in this drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Midscale</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3620</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>ES|Madrid|midscale</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Derived from hotel inventory · CoStar doesn't ship class-level KPIs in this drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>upper_midscale</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Upper Midscale</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3928</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>ES|Madrid|upper_midscale</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Derived from hotel inventory · CoStar doesn't ship class-level KPIs in this drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>upper_upscale</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Upper Upscale</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5739</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>ES|Madrid|upper_upscale</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Derived from hotel inventory · CoStar doesn't ship class-level KPIs in this drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>upscale</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Upscale</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>125</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>13431</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>ES|Madrid|upscale</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Derived from hotel inventory · CoStar doesn't ship class-level KPIs in this drop</t>
         </is>
       </c>
     </row>
@@ -1683,7 +2259,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Schema/rules version applied at ingestion time. Today: v1.1.</t>
+          <t>Schema/rules version applied at ingestion time. Today: v1.2.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2146,7 +2722,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-11T20:16:06+00:00. Normalization version: v1.1.</t>
+          <t>Built 2026-05-14T02:47:34+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>
@@ -2163,195 +2739,202 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx        — country aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx                  — country aggregates (Dataset A)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx    — market aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx              — market aggregates (Dataset A)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_SUBMERCADOS.xlsx — submarket aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_SUBMERCADOS.xlsx           — submarket aggregates (Dataset A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_CLASS.xlsx       — chain-scale time series (country or market level)</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_HOTELES_POR_MERCADO.xlsx   — hotel inventory (Dataset B · v1.2)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • COSTAR_MASTER_CLASS.xlsx                 — LEGACY (chain-scale aggregates · retired v1.2)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CompSet workbooks now live in the OPERATIONAL workspace at services/compset/</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t xml:space="preserve">  CompSet workbooks now live in the OPERATIONAL workspace at services/compset/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t xml:space="preserve">  (different purpose — hotel-specific underwriting outputs, not warehouse ingestion).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Operating contract:</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
+          <t>Operating contract:</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
+          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
+          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
+          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t xml:space="preserve">     in ingested_by + notes.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sheets:</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
+          <t>Sheets:</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
+          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
+          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
+          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • README            — this sheet</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Reference docs:</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-class-schema.md</t>
+          <t>Reference docs:</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-class-schema.md</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • docs/intelligence/costar-ingestion-workflow.md</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-    </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Regenerating this workbook:</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  python services/costar/scripts/build_masters.py</t>
+          <t>Regenerating this workbook:</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  python services/costar/scripts/build_masters.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Idempotent. Run when the schema evolves; commit both the script and the regenerated .xlsx.)</t>
         </is>

--- a/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -758,7 +758,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -950,7 +950,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1238,7 +1238,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T02:47:34+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T02:59:23+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_976be391c94a4aae</t>
+          <t>batch_43847c5c0d554445</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -758,7 +758,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-14T02:59:23+00:00</t>
+          <t>2026-05-14T03:06:34+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_976be391c94a4aae</t>
+          <t>batch_43847c5c0d554445</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-14T02:59:23+00:00</t>
+          <t>2026-05-14T03:06:34+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_976be391c94a4aae</t>
+          <t>batch_43847c5c0d554445</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -950,7 +950,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-14T02:59:23+00:00</t>
+          <t>2026-05-14T03:06:34+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_976be391c94a4aae</t>
+          <t>batch_43847c5c0d554445</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-14T02:59:23+00:00</t>
+          <t>2026-05-14T03:06:34+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_976be391c94a4aae</t>
+          <t>batch_43847c5c0d554445</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-14T02:59:23+00:00</t>
+          <t>2026-05-14T03:06:34+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_976be391c94a4aae</t>
+          <t>batch_43847c5c0d554445</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1238,7 +1238,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-14T02:59:23+00:00</t>
+          <t>2026-05-14T03:06:34+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T02:59:23+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:06:58+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -758,7 +758,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -950,7 +950,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1238,7 +1238,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:06:58+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:16:15+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -758,7 +758,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -950,7 +950,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1238,7 +1238,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:16:15+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:23:25+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -758,7 +758,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -950,7 +950,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1238,7 +1238,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:23:25+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:50:20+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y2" t="n">
-        <v>2965</v>
+        <v>2743</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -758,7 +758,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="X3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y3" t="n">
-        <v>3869</v>
+        <v>2565</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="X4" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Y4" t="n">
-        <v>3620</v>
+        <v>2879</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -950,7 +950,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1018,10 +1018,10 @@
         </is>
       </c>
       <c r="X5" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Y5" t="n">
-        <v>3928</v>
+        <v>3042</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="X6" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="Y6" t="n">
-        <v>5739</v>
+        <v>2497</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="X7" t="n">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="Y7" t="n">
-        <v>13431</v>
+        <v>8073</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1238,7 +1238,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:50:20+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-20T00:13:57+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_CLASS.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -758,7 +758,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -950,7 +950,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1238,7 +1238,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-20T00:13:57+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-20T00:48:39+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>
